--- a/packages/importer/fixtures/sample-register-anonymised.xlsx
+++ b/packages/importer/fixtures/sample-register-anonymised.xlsx
@@ -106,7 +106,7 @@
     <t>Kestrel Metals Group/ Kestrel Aluminium/ Plant</t>
   </si>
   <si>
-    <t>India/ West Bengal/ Belur</t>
+    <t>India/ West Bengal/ Riverbend</t>
   </si>
   <si>
     <t>Person Alpha</t>
@@ -1057,7 +1057,7 @@
     <t>Environment Module</t>
   </si>
   <si>
-    <t>Kestrel Aluminium Limited, Belur , Renewal of Consent to Operate under Water (Prevention and Control of Pollution) Act and Air (Prevention and Control of Pollution) Act</t>
+    <t>Kestrel Aluminium Limited, Riverbend , Renewal of Consent to Operate under Water (Prevention and Control of Pollution) Act and Air (Prevention and Control of Pollution) Act</t>
   </si>
   <si>
     <t>Super Critical</t>

--- a/packages/importer/fixtures/sample-register-anonymised.xlsx
+++ b/packages/importer/fixtures/sample-register-anonymised.xlsx
@@ -1710,7 +1710,7 @@
     <t>Pay to the Welfare Commissioner, employer's and employees' contribution, half yearly, before 15th July and 15th January every year in Form D.</t>
   </si>
   <si>
-    <t>No TDS deducted for Unionised employees for the month of June 2022. For Mgm employees TDS deposited by Renukoot</t>
+    <t>No TDS deducted for Unionised employees for the month of June 2022. For Mgm employees TDS deposited by Kestrelganj</t>
   </si>
   <si>
     <t>No TDS figure generated for Unionised emp for the month of Jul 2022 and for Mgm emp TDS directly deposited by Central Payroll Team</t>
@@ -1725,7 +1725,7 @@
     <t>We do not store any flammable gas in pressure vessel</t>
   </si>
   <si>
-    <t>No TDS appear for Unionised emp for Mgm emp TDS deposited by Renukoot</t>
+    <t>No TDS appear for Unionised emp for Mgm emp TDS deposited by Kestrelganj</t>
   </si>
   <si>
     <t>Overtime payment with Wages done</t>
@@ -1821,7 +1821,7 @@
     <t>complete</t>
   </si>
   <si>
-    <t xml:space="preserve">No TDS for Unionised emp for Management emp TDS deposited by Renukoot
+    <t xml:space="preserve">No TDS for Unionised emp for Management emp TDS deposited by Kestrelganj
 </t>
   </si>
   <si>
